--- a/data/trans_orig/IP07A09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18554</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30411</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51738</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90336</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56932</t>
+          <t>57494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97211</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126539</t>
+          <t>126476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103900</t>
+          <t>102385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127228</t>
+          <t>125818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115817</t>
+          <t>116429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140413</t>
+          <t>140275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226357</t>
+          <t>225335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>259477</t>
+          <t>258475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>32340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>49769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>36397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52340</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>70406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69518</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>132525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>80532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107756</t>
+          <t>107787</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161759</t>
+          <t>159308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>197985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>182132</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168651</t>
+          <t>169518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>199292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332172</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374275</t>
+          <t>373044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13219</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37924</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53554</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69959</t>
+          <t>69980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51601</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60442</t>
+          <t>58599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76518</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102954</t>
+          <t>105528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64162</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58857</t>
+          <t>57461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87327</t>
+          <t>87910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>115725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>87847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112735</t>
+          <t>111783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105746</t>
+          <t>106765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131218</t>
+          <t>132087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202008</t>
+          <t>201626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237511</t>
+          <t>237084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38564</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>46533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65404</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57180</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81200</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148332</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>92671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56556</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>144453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>173962</t>
+          <t>173556</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>165431</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>194380</t>
+          <t>195152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316022</t>
+          <t>316210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>358680</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43306</t>
+          <t>43665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52978</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38505</t>
+          <t>38707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>77134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106575</t>
+          <t>106535</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59368</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84771</t>
+          <t>84134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56833</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79928</t>
+          <t>79558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123105</t>
+          <t>123544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156532</t>
+          <t>157639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108395</t>
+          <t>107277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133980</t>
+          <t>135160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103694</t>
+          <t>105096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129982</t>
+          <t>130110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219424</t>
+          <t>221196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258299</t>
+          <t>257126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>27610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44948</t>
+          <t>44800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>26448</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51414</t>
+          <t>51242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36424</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>78178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156118</t>
+          <t>156642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87837</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116149</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175493</t>
+          <t>176758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>183003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>159487</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>192044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>320986</t>
+          <t>319149</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>363224</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
